--- a/team-management/process/年中绩效沟通表.xlsx
+++ b/team-management/process/年中绩效沟通表.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="年中绩效沟通记录表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="团队绩效汇总与档级校准" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="面谈准备清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AI时代潜力评估" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="面谈准备清单" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +92,16 @@
       <color rgb="00475569"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -135,7 +146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -157,11 +168,55 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -261,6 +316,56 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -668,18 +773,18 @@
           <t>姓名</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="36" t="n"/>
       <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="36" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>工号</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
+      <c r="G5" s="36" t="n"/>
       <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="5" t="n"/>
+      <c r="I5" s="36" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -687,18 +792,18 @@
           <t>部门</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
+      <c r="B6" s="36" t="n"/>
       <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="36" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>岗位 / 职级</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
+      <c r="G6" s="36" t="n"/>
       <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="5" t="n"/>
+      <c r="I6" s="36" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -706,18 +811,18 @@
           <t>入职日期</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="36" t="n"/>
       <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="36" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>直接主管</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="36" t="n"/>
       <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="5" t="n"/>
+      <c r="I7" s="36" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -725,18 +830,18 @@
           <t>沟通日期</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
+      <c r="B8" s="36" t="n"/>
       <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="36" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>沟通地点</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
+      <c r="G8" s="36" t="n"/>
       <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="5" t="n"/>
+      <c r="I8" s="36" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -793,7 +898,7 @@
       </c>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
+      <c r="D11" s="36" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
@@ -806,7 +911,7 @@
       </c>
       <c r="B12" s="12" t="n"/>
       <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
+      <c r="D12" s="36" t="n"/>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
@@ -819,7 +924,7 @@
       </c>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
+      <c r="D13" s="36" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
@@ -832,7 +937,7 @@
       </c>
       <c r="B14" s="12" t="n"/>
       <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
+      <c r="D14" s="36" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="11" t="n"/>
@@ -845,7 +950,7 @@
       </c>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="D15" s="36" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
@@ -858,9 +963,9 @@
           <t>权重合计（应为 100%）</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="36" t="n"/>
       <c r="E16" s="14">
         <f>SUM(E11:E15)</f>
         <v/>
@@ -869,9 +974,9 @@
         <f>IF(E16=100,"✓ 合计正确","当前合计 "&amp;E16&amp;"%，请确认")</f>
         <v/>
       </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
+      <c r="G16" s="37" t="n"/>
+      <c r="H16" s="37" t="n"/>
+      <c r="I16" s="36" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -923,13 +1028,13 @@
           <t>业绩产出</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
+      <c r="B19" s="36" t="n"/>
       <c r="C19" s="17" t="inlineStr">
         <is>
           <t>目标达成度、工作质量、交付效率</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="36" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -945,13 +1050,13 @@
           <t>专业能力</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
+      <c r="B20" s="36" t="n"/>
       <c r="C20" s="20" t="inlineStr">
         <is>
           <t>技术深度、问题解决、创新能力</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n"/>
+      <c r="D20" s="36" t="n"/>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="11" t="n"/>
@@ -967,13 +1072,13 @@
           <t>团队协作</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
+      <c r="B21" s="36" t="n"/>
       <c r="C21" s="17" t="inlineStr">
         <is>
           <t>沟通配合、知识分享、帮助他人</t>
         </is>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="36" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -989,13 +1094,13 @@
           <t>主动性</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n"/>
+      <c r="B22" s="36" t="n"/>
       <c r="C22" s="20" t="inlineStr">
         <is>
           <t>积极思考、主动承担、推动改进</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n"/>
+      <c r="D22" s="36" t="n"/>
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="11" t="n"/>
       <c r="G22" s="11" t="n"/>
@@ -1011,13 +1116,13 @@
           <t>成长发展</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
+      <c r="B23" s="36" t="n"/>
       <c r="C23" s="17" t="inlineStr">
         <is>
           <t>学习提升、技能拓展、能力进阶</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="36" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
@@ -1033,11 +1138,11 @@
           <t>能力综合得分（按权重加权，5 分制）</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="36" t="n"/>
       <c r="G24" s="22">
         <f>IFERROR(SUMPRODUCT(E19:E23,G19:G23)/SUM(E19:E23),"")</f>
         <v/>
@@ -1047,7 +1152,7 @@
           <t>参考：≥4.5 卓越 ｜ 4–4.5 优秀 ｜ 3–4 合格 ｜ &lt;3 待提升</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n"/>
+      <c r="I24" s="36" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -1079,14 +1184,14 @@
           <t>亮点 1</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
+      <c r="B27" s="36" t="n"/>
       <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="D27" s="37" t="n"/>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="36" t="n"/>
       <c r="G27" s="6" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
+      <c r="H27" s="37" t="n"/>
+      <c r="I27" s="36" t="n"/>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -1094,14 +1199,14 @@
           <t>亮点 2</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
+      <c r="B28" s="36" t="n"/>
       <c r="C28" s="6" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="D28" s="37" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="36" t="n"/>
       <c r="G28" s="6" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
+      <c r="H28" s="37" t="n"/>
+      <c r="I28" s="36" t="n"/>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -1109,14 +1214,14 @@
           <t>亮点 3</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
+      <c r="B29" s="36" t="n"/>
       <c r="C29" s="6" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
+      <c r="D29" s="37" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="36" t="n"/>
       <c r="G29" s="6" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
+      <c r="H29" s="37" t="n"/>
+      <c r="I29" s="36" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -1131,18 +1236,18 @@
           <t>B ｜ 行为</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
+      <c r="B31" s="36" t="n"/>
       <c r="C31" s="15" t="inlineStr">
         <is>
           <t>客观描述具体行为和事实，不加评判（例：最近三个迭代，有两次延期交付）</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
+      <c r="D31" s="37" t="n"/>
+      <c r="E31" s="37" t="n"/>
+      <c r="F31" s="37" t="n"/>
+      <c r="G31" s="37" t="n"/>
+      <c r="H31" s="37" t="n"/>
+      <c r="I31" s="36" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
@@ -1150,18 +1255,18 @@
           <t>E ｜ 影响</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
+      <c r="B32" s="36" t="n"/>
       <c r="C32" s="15" t="inlineStr">
         <is>
           <t>说明该行为带来的影响和后果（例：导致下游测试团队工作被打乱）</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
+      <c r="D32" s="37" t="n"/>
+      <c r="E32" s="37" t="n"/>
+      <c r="F32" s="37" t="n"/>
+      <c r="G32" s="37" t="n"/>
+      <c r="H32" s="37" t="n"/>
+      <c r="I32" s="36" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="25" t="inlineStr">
@@ -1169,18 +1274,18 @@
           <t>S ｜ 建议</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
+      <c r="B33" s="36" t="n"/>
       <c r="C33" s="15" t="inlineStr">
         <is>
           <t>给出具体的改进建议和方向（例：排期时预留 20% buffer）</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
+      <c r="D33" s="37" t="n"/>
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="37" t="n"/>
+      <c r="G33" s="37" t="n"/>
+      <c r="H33" s="37" t="n"/>
+      <c r="I33" s="36" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="25" t="inlineStr">
@@ -1188,18 +1293,18 @@
           <t>T ｜ 信任</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
+      <c r="B34" s="36" t="n"/>
       <c r="C34" s="15" t="inlineStr">
         <is>
           <t>表达对员工改进的信心与期待（例：以你的能力，调整后一定能做好）</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
+      <c r="D34" s="37" t="n"/>
+      <c r="E34" s="37" t="n"/>
+      <c r="F34" s="37" t="n"/>
+      <c r="G34" s="37" t="n"/>
+      <c r="H34" s="37" t="n"/>
+      <c r="I34" s="36" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -1240,11 +1345,11 @@
         <v>1</v>
       </c>
       <c r="B37" s="10" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
+      <c r="C37" s="37" t="n"/>
+      <c r="D37" s="36" t="n"/>
       <c r="E37" s="10" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
+      <c r="F37" s="37" t="n"/>
+      <c r="G37" s="36" t="n"/>
       <c r="H37" s="8" t="n"/>
       <c r="I37" s="8" t="n"/>
     </row>
@@ -1253,11 +1358,11 @@
         <v>2</v>
       </c>
       <c r="B38" s="13" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
+      <c r="C38" s="37" t="n"/>
+      <c r="D38" s="36" t="n"/>
       <c r="E38" s="13" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
+      <c r="F38" s="37" t="n"/>
+      <c r="G38" s="36" t="n"/>
       <c r="H38" s="11" t="n"/>
       <c r="I38" s="11" t="n"/>
     </row>
@@ -1266,11 +1371,11 @@
         <v>3</v>
       </c>
       <c r="B39" s="10" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
+      <c r="C39" s="37" t="n"/>
+      <c r="D39" s="36" t="n"/>
       <c r="E39" s="10" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
+      <c r="F39" s="37" t="n"/>
+      <c r="G39" s="36" t="n"/>
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="8" t="n"/>
     </row>
@@ -1279,11 +1384,11 @@
         <v>4</v>
       </c>
       <c r="B40" s="13" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="n"/>
+      <c r="C40" s="37" t="n"/>
+      <c r="D40" s="36" t="n"/>
       <c r="E40" s="13" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
+      <c r="F40" s="37" t="n"/>
+      <c r="G40" s="36" t="n"/>
       <c r="H40" s="11" t="n"/>
       <c r="I40" s="11" t="n"/>
     </row>
@@ -1292,11 +1397,11 @@
         <v>5</v>
       </c>
       <c r="B41" s="10" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
+      <c r="C41" s="37" t="n"/>
+      <c r="D41" s="36" t="n"/>
       <c r="E41" s="10" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
+      <c r="F41" s="37" t="n"/>
+      <c r="G41" s="36" t="n"/>
       <c r="H41" s="8" t="n"/>
       <c r="I41" s="8" t="n"/>
     </row>
@@ -1313,14 +1418,14 @@
           <t>重点发展能力</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n"/>
+      <c r="B43" s="36" t="n"/>
       <c r="C43" s="6" t="inlineStr"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
+      <c r="D43" s="37" t="n"/>
+      <c r="E43" s="37" t="n"/>
+      <c r="F43" s="37" t="n"/>
+      <c r="G43" s="37" t="n"/>
+      <c r="H43" s="37" t="n"/>
+      <c r="I43" s="36" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
@@ -1328,18 +1433,18 @@
           <t>70% ｜ 工作实践</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n"/>
+      <c r="B44" s="36" t="n"/>
       <c r="C44" s="15" t="inlineStr">
         <is>
           <t>挑战性项目、扩大职责范围、跨团队协作、试错与复盘</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
+      <c r="D44" s="37" t="n"/>
+      <c r="E44" s="37" t="n"/>
+      <c r="F44" s="37" t="n"/>
+      <c r="G44" s="37" t="n"/>
+      <c r="H44" s="37" t="n"/>
+      <c r="I44" s="36" t="n"/>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
@@ -1347,18 +1452,18 @@
           <t>20% ｜ 交流讨论</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
+      <c r="B45" s="36" t="n"/>
       <c r="C45" s="15" t="inlineStr">
         <is>
           <t>导师辅导、技术分享、Code Review、团队讨论与头脑风暴</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
+      <c r="D45" s="37" t="n"/>
+      <c r="E45" s="37" t="n"/>
+      <c r="F45" s="37" t="n"/>
+      <c r="G45" s="37" t="n"/>
+      <c r="H45" s="37" t="n"/>
+      <c r="I45" s="36" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
@@ -1366,18 +1471,18 @@
           <t>10% ｜ 培训自学</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n"/>
+      <c r="B46" s="36" t="n"/>
       <c r="C46" s="15" t="inlineStr">
         <is>
           <t>培训课程、技术书籍、在线课程、技术大会</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
+      <c r="D46" s="37" t="n"/>
+      <c r="E46" s="37" t="n"/>
+      <c r="F46" s="37" t="n"/>
+      <c r="G46" s="37" t="n"/>
+      <c r="H46" s="37" t="n"/>
+      <c r="I46" s="36" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
@@ -1385,18 +1490,18 @@
           <t>预期成果</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n"/>
+      <c r="B47" s="36" t="n"/>
       <c r="C47" s="15" t="inlineStr">
         <is>
           <t>可衡量的阶段性成果（如独立负责某模块、输出某项技术方案）</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
+      <c r="D47" s="37" t="n"/>
+      <c r="E47" s="37" t="n"/>
+      <c r="F47" s="37" t="n"/>
+      <c r="G47" s="37" t="n"/>
+      <c r="H47" s="37" t="n"/>
+      <c r="I47" s="36" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
@@ -1411,18 +1516,18 @@
           <t>拟定绩效档级</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n"/>
+      <c r="B49" s="36" t="n"/>
       <c r="C49" s="15" t="inlineStr">
         <is>
           <t>S / A / B / C / D</t>
         </is>
       </c>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
+      <c r="D49" s="37" t="n"/>
+      <c r="E49" s="37" t="n"/>
+      <c r="F49" s="37" t="n"/>
+      <c r="G49" s="37" t="n"/>
+      <c r="H49" s="37" t="n"/>
+      <c r="I49" s="36" t="n"/>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -1430,14 +1535,14 @@
           <t>双方达成的共识</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n"/>
+      <c r="B50" s="36" t="n"/>
       <c r="C50" s="6" t="inlineStr"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
+      <c r="D50" s="37" t="n"/>
+      <c r="E50" s="37" t="n"/>
+      <c r="F50" s="37" t="n"/>
+      <c r="G50" s="37" t="n"/>
+      <c r="H50" s="37" t="n"/>
+      <c r="I50" s="36" t="n"/>
     </row>
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -1445,14 +1550,14 @@
           <t>员工意见 / 想法</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n"/>
+      <c r="B51" s="36" t="n"/>
       <c r="C51" s="6" t="inlineStr"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
+      <c r="D51" s="37" t="n"/>
+      <c r="E51" s="37" t="n"/>
+      <c r="F51" s="37" t="n"/>
+      <c r="G51" s="37" t="n"/>
+      <c r="H51" s="37" t="n"/>
+      <c r="I51" s="36" t="n"/>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
@@ -1460,18 +1565,18 @@
           <t>员工签字：__________    日期：__________</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
+      <c r="B52" s="37" t="n"/>
+      <c r="C52" s="37" t="n"/>
+      <c r="D52" s="37" t="n"/>
+      <c r="E52" s="36" t="n"/>
       <c r="F52" s="26" t="inlineStr">
         <is>
           <t>管理者签字：__________    日期：__________</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
+      <c r="G52" s="37" t="n"/>
+      <c r="H52" s="37" t="n"/>
+      <c r="I52" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="121">
@@ -2087,6 +2192,365 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>AI时代员工潜力评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>能力层看'现在用得怎么样'，特质层看'未来能走多远'。1-5 分制：高/中高/中/中低/低。重点不是'用了多少AI工具'，而是'用AI产出了什么价值、沉淀了什么经验'。低分是培养信号，不是淘汰依据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="C3" s="39" t="inlineStr">
+        <is>
+          <t>一句话定义</t>
+        </is>
+      </c>
+      <c r="D3" s="39" t="inlineStr">
+        <is>
+          <t>评估等级</t>
+        </is>
+      </c>
+      <c r="E3" s="39" t="inlineStr">
+        <is>
+          <t>评分</t>
+        </is>
+      </c>
+      <c r="F3" s="39" t="inlineStr">
+        <is>
+          <t>行为依据 / 具体事例</t>
+        </is>
+      </c>
+      <c r="G3" s="39" t="inlineStr">
+        <is>
+          <t>潜力判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>能力层</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>人机协同能力</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>把AI系统化融入个人工作流，以任务拆解和提示词调动AI，以独立判断兜底，并沉淀为团队资产</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>高=用活AI(带动组织提效) / 中高=用好AI(有标杆) / 中=能用AI(基础出活) / 中低=用过AI(短板明显) / 低=排斥无判断</t>
+        </is>
+      </c>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="44" t="n"/>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>特质层</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>善于思考（判断力）</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="inlineStr">
+        <is>
+          <t>不盲信AI输出，能识别边界、风险和异常，做出有依据的取舍判断</t>
+        </is>
+      </c>
+      <c r="D5" s="47" t="inlineStr">
+        <is>
+          <t>高=识别系统性风险且影响他人 / 中高=主动识别边界风险 / 中=主动质疑说明理由 / 中低=有质疑但理由不足 / 低=照单全收</t>
+        </is>
+      </c>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="48" t="n"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>特质层</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>勤于自省（认知开放）</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>面对新范式愿意先理解再判断，能修正旧认知，不把过去成功绝对化</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>高=范式级迭代并带动团队 / 中高=主动找不同观点并推翻结论 / 中=被告知后能跟上 / 中低=知道但不调整 / 低=封闭防御</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="44" t="n"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>特质层</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>追求卓越（好奇心）</t>
+        </is>
+      </c>
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t>对新工具有探索欲，学习敏捷，能迁移到真实场景，从失败中提炼新规则</t>
+        </is>
+      </c>
+      <c r="D7" s="47" t="inlineStr">
+        <is>
+          <t>高=跨领域迁移产生乘数效应 / 中高=形成方法论效率领先 / 中=有真实应用 / 中低=浅尝辄止 / 低=排斥探索</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="48" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t>综合潜力判断（建议结合1对1长期观察，看趋势而非单次）</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="50">
+        <f>IFERROR(AVERAGE(E4:E7),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>≥4.0 高潜力 ｜ 3.0-4.0 有潜力 ｜ &lt;3.0 需重点培养</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="51" t="inlineStr">
+        <is>
+          <t>人机协同能力的五个子能力（用于细化评分依据）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>技术判断力</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="52" t="inlineStr">
+        <is>
+          <t>不轻信AI输出，能识别系统性风险（不只是个案错误），关键节点有质量兜底意识</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>问题拆解</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>为复杂模糊问题设计可行路径，给AI明确的上下文和任务边界</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>工具驾驭</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="52" t="inlineStr">
+        <is>
+          <t>上下文投喂精准，指令边界明确，出错后能小步修正直指原因</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>AI技术理解</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>理解AI能力边界，有RAG/Agent等工程实践经验，知道哪些场景适合AI重塑</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>贡献</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="52" t="inlineStr">
+        <is>
+          <t>把个人实践沉淀为团队经验，推动整体提效——这是区分'中高'与'高'的关键</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>在绩效沟通中的应用提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="53" t="inlineStr">
+        <is>
+          <t>• 绩效制定：把'人机协同能力'作为专业/能力目标之一（如：本季度用AI重构某项重复工作流）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="53" t="inlineStr">
+        <is>
+          <t>• 绩效评估：用五级标准给AI能力打分，重点关注'贡献'子能力——是否沉淀为团队资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="53" t="inlineStr">
+        <is>
+          <t>• 绩效沟通：特质层用于讨论'未来潜力'，倾听员工对AI的态度，判断是主动迭代还是被动防御</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>• 能力培养(7-2-1)：70%安排真实AI业务问题 / 20%结对使用与交流 / 10%学习资源</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="53" t="inlineStr">
+        <is>
+          <t>• 低分不等于淘汰：先问'为什么'，可能是没找到切入点或工具不顺手，作为培养计划输入</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="C13:G13"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="E4 E5 E6 E7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"5,4,3,2,1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"高潜力,有潜力,需重点培养,待观察"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/team-management/process/年中绩效沟通表.xlsx
+++ b/team-management/process/年中绩效沟通表.xlsx
@@ -441,6 +441,198 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -727,7 +919,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1719,11 +1911,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2183,11 +2376,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2542,11 +2736,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2851,5 +3046,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>